--- a/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="92">
   <si>
     <t>OCG</t>
   </si>
@@ -2795,10 +2795,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>21000</v>
+        <v>20700</v>
       </c>
       <c r="E43" s="3">
-        <v>21000</v>
+        <v>20700</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
@@ -2930,11 +2930,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
       </c>
       <c r="F45" s="3">
         <v>11800</v>
@@ -3799,10 +3799,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F59" s="3">
         <v>600</v>
